--- a/法条关联表 完整版.xlsx
+++ b/法条关联表 完整版.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Onesummer_D\Learning\Competitons\TiaoZhanBei\项目\法学产出物\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358A7F50-2F28-4675-92B1-A34BD8891A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4990" yWindow="3220" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="20752" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="法条名称" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="176">
   <si>
     <t>关联线索类型</t>
   </si>
@@ -45,6 +39,9 @@
   </si>
   <si>
     <t>关联场景（12345高频投诉类型）</t>
+  </si>
+  <si>
+    <t>列1</t>
   </si>
   <si>
     <t>刑事犯罪</t>
@@ -59,6 +56,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>恶意拨打</t>
     </r>
     <r>
@@ -66,7 +70,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>12345</t>
     </r>
@@ -89,6 +93,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>以拨打</t>
     </r>
     <r>
@@ -96,7 +107,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>12345</t>
     </r>
@@ -114,7 +125,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>“</t>
     </r>
@@ -132,7 +143,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>”</t>
     </r>
@@ -166,6 +177,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>通过</t>
     </r>
     <r>
@@ -173,7 +191,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>12345</t>
     </r>
@@ -206,6 +224,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -226,6 +251,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -250,6 +282,174 @@
 超期羁押</t>
   </si>
   <si>
+    <t>《刑法》第一百三十三条</t>
+  </si>
+  <si>
+    <t>违反交通运输管理法规，因而发生重大事故，致人重伤、死亡或者使公私财产遭受重大损失的，处三年以下有期徒刑或者拘役；交通运输肇事后逃逸或者有其他特别恶劣情节的，处三年以上七年以下有期徒刑；因逃逸致人死亡的，处七年以上有期徒刑。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的交通事故致人伤亡、肇事逃逸等严重交通违法行为</t>
+  </si>
+  <si>
+    <t>《刑法》第一百三十三条之一</t>
+  </si>
+  <si>
+    <t>在道路上驾驶机动车，有下列情形之一的，处拘役，并处罚金：（一）追逐竞驶，情节恶劣的；（二）醉酒驾驶机动车的；（三）从事校车业务或者旅客运输，严重超过额定乘员载客，或者严重超过规定时速行驶的；（四）违反危险化学品安全管理规定运输危险化学品，危及公共安全的。机动车所有人、管理人对前款第三项、第四项行为负有直接责任的，依照前款的规定处罚。有前两款行为，同时构成其他犯罪的，依照处罚较重的规定定罪处罚。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的飙车炸街、醉酒驾驶、校车超载等危害公共安全的交通违法行为</t>
+  </si>
+  <si>
+    <t>《刑法》第一百三十三条之二</t>
+  </si>
+  <si>
+    <t>对行驶中的公共交通工具的驾驶人员使用暴力或者抢控驾驶操纵装置，干扰公共交通工具正常行驶，危及公共安全的，处一年以下有期徒刑、拘役或者管制，并处或者单处罚金。前款规定的驾驶人员在行驶的公共交通工具上擅离职守，与他人互殴或者殴打他人，危及公共安全的，依照前款的规定处罚。有前两款行为，同时构成其他犯罪的，依照处罚较重的规定定罪处罚。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的乘客抢夺公交车方向盘、殴打公交司机、干扰司机驾驶等危害公共交通安全的行为</t>
+  </si>
+  <si>
+    <t>《刑法》第一百三十四条</t>
+  </si>
+  <si>
+    <t>在生产、作业中违反有关安全管理的规定，因而发生重大伤亡事故或者造成其他严重后果的，处三年以下有期徒刑或者拘役；情节特别恶劣的，处三年以上七年以下有期徒刑。强令他人违章冒险作业，或者明知存在重大事故隐患而不排除，仍冒险组织作业，因而发生重大伤亡事故或者造成其他严重后果的，处五年以下有期徒刑或者拘役；情节特别恶劣的，处五年以上有期徒刑。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的工地安全事故、电梯坠落致人伤亡、锅炉爆炸、危险化学品泄漏、建筑施工坍塌等安全生产事故</t>
+  </si>
+  <si>
+    <t>《刑法》第一百一十五条第二款</t>
+  </si>
+  <si>
+    <t>过失犯前款罪的，处三年以上七年以下有期徒刑；情节较轻的，处三年以下有期徒刑或者拘役。注：第一款为放火、决水、爆炸以及投放毒害性、放射性、传染病病原体等物质或者以其他危险方法致人重伤、死亡或者使公私财产遭受重大损失，处十年以上有期徒刑、无期徒刑或者死刑。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的山林失火、野外用火引发火灾、楼道堆放杂物引发火灾致人伤亡等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第一百四十条</t>
+  </si>
+  <si>
+    <t>生产者、销售者在产品中掺杂、掺假，以假充真，以次充好或者以不合格产品冒充合格产品，销售金额五万元以上不满二十万元的，处二年以下有期徒刑或者拘役，并处或者单处销售金额百分之五十以上二倍以下罚金；销售金额二十万元以上不满五十万元的，处二年以上七年以下有期徒刑，并处销售金额百分之五十以上二倍以下罚金；销售金额五十万元以上不满二百万元的，处七年以上有期徒刑，并处销售金额百分之五十以上二倍以下罚金；销售金额二百万元以上的，处十五年有期徒刑或者无期徒刑，并处销售金额百分之五十以上二倍以下罚金或者没收财产。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的买到假烟假酒、假冒名牌商品、劣质化肥农药种子、建材以次充好等消费维权问题</t>
+  </si>
+  <si>
+    <t>《刑法》第二百一十三条</t>
+  </si>
+  <si>
+    <t>未经注册商标所有人许可，在同一种商品、服务上使用与其注册商标相同的商标，情节严重的，处三年以下有期徒刑，并处或者单处罚金；情节特别严重的，处三年以上十年以下有期徒刑，并处罚金。注：《刑法修正案（十一）》对本条进行了修订，将法定最高刑从七年提高至十年，并增加了“服务”商标的保护。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的假名牌运动鞋、仿冒奢侈品、山寨电子产品、假冒化妆品等侵犯商标权行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百五十三条之一</t>
+  </si>
+  <si>
+    <t>违反国家有关规定，向他人出售或者提供公民个人信息，情节严重的，处三年以下有期徒刑或者拘役，并处或者单处罚金；情节特别严重的，处三年以上七年以下有期徒刑，并处罚金。违反国家有关规定，将在履行职责或者提供服务过程中获得的公民个人信息，出售或者提供给他人的，依照前款的规定从重处罚。窃取或者以其他方法非法获取公民个人信息的，依照第一款的规定处罚。单位犯前三款罪的，对单位判处罚金，并对其直接负责的主管人员和其他直接责任人员，依照各该款的规定处罚。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的骚扰电话泄露个人信息、快递单泄露隐私、物业出售业主信息、中介倒卖客户信息等侵犯公民个人信息行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百六十条</t>
+  </si>
+  <si>
+    <t>虐待家庭成员，情节恶劣的，处二年以下有期徒刑、拘役或者管制。犯前款罪，致使被害人重伤、死亡的，处二年以上七年以下有期徒刑。第一款罪，告诉的才处理，但被害人没有能力告诉，或者因受到强制、威吓无法告诉的除外。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的子女虐待老人、父母虐待儿童、配偶家暴长期虐待、护工虐待被看护人等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百六十四条</t>
+  </si>
+  <si>
+    <t>盗窃公私财物，数额较大的，或者多次盗窃、入户盗窃、携带凶器盗窃、扒窃的，处三年以下有期徒刑、拘役或者管制，并处或者单处罚金；数额巨大或者有其他严重情节的，处三年以上十年以下有期徒刑，并处罚金；数额特别巨大或者有其他特别严重情节的，处十年以上有期徒刑或者无期徒刑，并处罚金或者没收财产。注：根据“两高”《关于办理盗窃刑事案件适用法律若干问题的解释》，数额较大标准为1000元至3000元以上，数额巨大标准为3万元至10万元以上，数额特别巨大标准为30万元至50万元以上。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的财物被盗、电动车电瓶被盗、装修材料被盗等财产损失事件</t>
+  </si>
+  <si>
+    <t>《刑法》第二百七十一条</t>
+  </si>
+  <si>
+    <t>公司、企业或者其他单位的工作人员，利用职务上的便利，将本单位财物非法占为己有，数额较大的，处三年以下有期徒刑或者拘役，并处罚金；数额巨大的，处三年以上十年以下有期徒刑，并处罚金；数额特别巨大的，处十年以上有期徒刑或者无期徒刑，并处罚金。注：《刑法修正案（十一）》对本条进行了修订，增设了“数额特别巨大”一档法定刑，最高刑提升至无期徒刑。入罪数额标准为3万元以上。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的公司员工挪用公款、物业人员侵占公共收益、村干部侵占集体资产、财务人员贪污等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百七十七条</t>
+  </si>
+  <si>
+    <t>以暴力、威胁方法阻碍国家机关工作人员依法执行职务的，处三年以下有期徒刑、拘役、管制或者罚金。暴力袭击正在依法执行职务的人民警察的，处三年以下有期徒刑、拘役或者管制；使用枪支、管制刀具，或者以驾驶机动车撞击等手段，严重危及其人身安全的，处三年以上七年以下有期徒刑。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的暴力抗法、阻碍城管执法、袭击警察等妨害公务行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百九十一条之二</t>
+  </si>
+  <si>
+    <t>从建筑物或者其他高空抛掷物品，情节严重的，处一年以下有期徒刑、拘役或者管制，并处或者单处罚金。有前款行为，同时构成其他犯罪的，依照处罚较重的规定定罪处罚。注：本条文系《刑法修正案（十一）》新增。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的高空抛物砸坏车辆或伤人、抛物致人受伤等危害公共安全行为</t>
+  </si>
+  <si>
+    <t>《刑法》第三百二十四条第一款</t>
+  </si>
+  <si>
+    <t>故意损毁国家保护的珍贵文物或者被确定为全国重点文物保护单位、省级文物保护单位的文物的，处三年以下有期徒刑或者拘役，并处或者单处罚金；情节严重的，处三年以上十年以下有期徒刑，并处罚金。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的古墓被盗掘、文物被破坏、历史建筑被拆毁、文物保护区被违法施工等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第三百二十八条第一款</t>
+  </si>
+  <si>
+    <t>盗掘具有历史、艺术、科学价值的古文化遗址、古墓葬的，处三年以上十年以下有期徒刑，并处罚金；情节较轻的，处三年以下有期徒刑、拘役或者管制，并处罚金；有下列情形之一的，处十年以上有期徒刑或者无期徒刑，并处罚金或者没收财产：（一）盗掘确定为全国重点文物保护单位和省级文物保护单位的古文化遗址、古墓葬的；（二）盗掘古文化遗址、古墓葬集团的首要分子；（三）多次盗掘古文化遗址、古墓葬的；（四）盗掘古文化遗址、古墓葬，并盗窃珍贵文物或者造成珍贵文物严重破坏的。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的古墓被盗、遗址被破坏、施工中发现文物未上报被私分等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第三百三十八条</t>
+  </si>
+  <si>
+    <t>违反国家规定，排放、倾倒或者处置有放射性的废物、含传染病病原体的废物、有毒物质或者其他有害物质，严重污染环境的，处三年以下有期徒刑或者拘役，并处或者单处罚金；情节严重的，处三年以上七年以下有期徒刑，并处罚金；有下列情形之一的，处七年以上有期徒刑，并处罚金：（一）在饮用水水源保护区、自然保护地核心保护区等依法确定的重点保护区域排放、倾倒、处置有放射性的废物，情节特别严重的；（二）向国家确定的重要江河、湖泊水域排放、倾倒、处置有放射性的废物，情节特别严重的；（三）致使大量永久基本农田基本功能丧失或者遭受永久性破坏的；（四）致使多人重伤、严重疾病，或者致人严重残疾、死亡的。注：《刑法修正案（十一）》对本条进行了修订，增加了法定刑档次，最高刑提升至七年以上有期徒刑。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的工厂偷排废水、化工厂排放有毒气体、养殖场直排粪污、倾倒危险废物等严重环境污染行为</t>
+  </si>
+  <si>
+    <t>《刑法》第三百四十一条第二款</t>
+  </si>
+  <si>
+    <t>违反狩猎法规，在禁猎区、禁猎期或者使用禁用的工具、方法进行狩猎，破坏野生动物资源，情节严重的，处三年以下有期徒刑、拘役、管制或者罚金。注：根据两高《关于办理破坏野生动物资源刑事案件适用法律若干问题的解释》，非法猎捕野生动物价值一万元以上，或在禁猎区、禁猎期使用禁用工具、方法狩猎的，以非法狩猎罪定罪处罚。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的非法捕鸟、电鱼、下网捕猎野生动物、破坏野生动物栖息地等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第三百四十三条第一款</t>
+  </si>
+  <si>
+    <t>违反矿产资源法的规定，未取得采矿许可证擅自采矿，擅自进入国家规划矿区、对国民经济具有重要价值的矿区和他人矿区范围采矿，或者擅自开采国家规定实行保护性开采的特定矿种，情节严重的，处三年以下有期徒刑、拘役或者管制，并处或者单处罚金；情节特别严重的，处三年以上七年以下有期徒刑，并处罚金。注：根据“两高”《关于办理非法采矿、破坏性采矿刑事案件适用法律若干问题的解释》，非法采矿造成矿产资源破坏价值5万元以上为“造成矿产资源破坏”，30万元以上为“造成矿产资源严重破坏”。</t>
+  </si>
+  <si>
+    <t>12345投诉中反映的非法采砂、私挖盗采山石、破坏山体、夜间非法采矿扰民等行为</t>
+  </si>
+  <si>
+    <t>《刑法》第二百九十一条之二（高空抛物罪）</t>
+  </si>
+  <si>
+    <t>从建筑物或者其他高空抛掷物品，情节严重的，处一年以下有期徒刑、拘役或者管制，并处或者单处罚金。有前款行为，同时构成其他犯罪的，依照处罚较重的规定定罪处罚。</t>
+  </si>
+  <si>
     <t>公益诉讼</t>
   </si>
   <si>
@@ -269,6 +469,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -295,6 +502,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>人民检察院行使下列职权：…</t>
     </r>
     <r>
@@ -318,6 +532,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -338,6 +559,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -382,6 +610,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>“</t>
     </r>
     <r>
@@ -398,7 +633,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>”</t>
     </r>
@@ -427,6 +662,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -441,6 +683,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>“</t>
     </r>
     <r>
@@ -457,7 +706,7 @@
         <sz val="12"/>
         <color rgb="FF000000"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>”</t>
     </r>
@@ -495,6 +744,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -515,6 +771,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -562,6 +825,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>人民检察院行使下列职权：</t>
     </r>
     <r>
@@ -569,7 +839,7 @@
         <sz val="12"/>
         <color indexed="8"/>
         <rFont val="Segoe UI"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>……</t>
     </r>
@@ -604,6 +874,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -642,6 +919,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -662,6 +946,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -669,7 +959,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t>投诉反映的行政违法行为涉嫌犯罪但未移送司法的情形</t>
     </r>
@@ -682,6 +972,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="0"/>
+      </rPr>
       <t>12345</t>
     </r>
     <r>
@@ -689,7 +985,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
+        <charset val="0"/>
       </rPr>
       <t>投诉反映行政诉讼中损害国家利益或审判人员违法的情形</t>
     </r>
@@ -749,16 +1045,18 @@
   <si>
     <t>12345投诉关于执法机关未说明理由或未听取意见的相关问题</t>
   </si>
-  <si>
-    <t>列1</t>
-    <phoneticPr fontId="11" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="12" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,12 +1087,169 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -806,35 +1261,10 @@
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -843,12 +1273,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79995117038483843"/>
-        <bgColor theme="4" tint="0.79995117038483843"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -864,10 +1480,10 @@
         <color theme="4"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -880,7 +1496,7 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -889,28 +1505,28 @@
         <color theme="4"/>
       </left>
       <right style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </left>
       <right style="thin">
         <color theme="4"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -922,7 +1538,7 @@
         <color theme="4"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
         <color theme="4"/>
@@ -931,13 +1547,13 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </left>
       <right style="thin">
         <color theme="4"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
         <color theme="4"/>
@@ -949,23 +1565,265 @@
         <color theme="4"/>
       </left>
       <right style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39994506668294322"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -975,33 +1833,39 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1011,9 +1875,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1045,208 +1906,201 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="30">
     <dxf>
       <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
         <color theme="1"/>
-        <name val="宋体"/>
-        <charset val="134"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="none"/>
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-      <alignment horizontal="left"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
-        <sz val="12"/>
+        <b val="1"/>
+        <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <sz val="12"/>
+        <b val="1"/>
+        <color theme="1"/>
       </font>
-      <alignment horizontal="left"/>
     </dxf>
     <dxf>
       <font>
-        <sz val="12"/>
+        <b val="1"/>
+        <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
       <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
+        <top style="double">
+          <color theme="4"/>
+        </top>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
+        <color theme="0"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
       <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
         <top style="thin">
           <color theme="4"/>
         </top>
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.599993896298105"/>
+          <bgColor theme="4" tint="0.599993896298105"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.599993896298105"/>
+          <bgColor theme="4" tint="0.599993896298105"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="宋体"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.59999389629810485"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.59999389629810485"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -1266,7 +2120,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
@@ -1276,8 +2130,8 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
       <border>
@@ -1294,157 +2148,210 @@
           <color theme="4"/>
         </bottom>
         <vertical style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </vertical>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="宋体"/>
+        <scheme val="none"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
       <border>
-        <top style="double">
-          <color theme="4"/>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
         </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="0"/>
+        <b val="1"/>
+        <color theme="1"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
       <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
         <bottom style="thin">
-          <color theme="4"/>
+          <color theme="4" tint="0.399975585192419"/>
         </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="5" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="29"/>
-      <tableStyleElement type="headerRow" dxfId="28"/>
-      <tableStyleElement type="totalRow" dxfId="27"/>
-      <tableStyleElement type="firstColumn" dxfId="26"/>
-      <tableStyleElement type="lastColumn" dxfId="25"/>
-      <tableStyleElement type="firstRowStripe" dxfId="24"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="23"/>
+      <tableStyleElement type="wholeTable" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstColumn" dxfId="8"/>
+      <tableStyleElement type="lastColumn" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="5"/>
     </tableStyle>
     <tableStyle name="TableStylePreset5_Accent1" pivot="0" count="7" xr9:uid="{F18FD337-1710-4A1D-B403-C7D32ECF9798}">
-      <tableStyleElement type="wholeTable" dxfId="22"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstColumn" dxfId="19"/>
-      <tableStyleElement type="lastColumn" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="18"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstColumn" dxfId="15"/>
+      <tableStyleElement type="lastColumn" dxfId="14"/>
+      <tableStyleElement type="firstRowStripe" dxfId="13"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="12"/>
     </tableStyle>
-    <tableStyle name="表样式 1" pivot="0" count="1" xr9:uid="{C3DB7085-A763-4F4F-BC6E-5861CCE54907}">
-      <tableStyleElement type="wholeTable" dxfId="15"/>
+    <tableStyle name="表样式 1" pivot="0" count="1" xr9:uid="{4250B03E-6E05-45B3-A074-4BCA87918FDA}">
+      <tableStyleElement type="wholeTable" dxfId="19"/>
     </tableStyle>
-    <tableStyle name="表样式 2" pivot="0" count="0" xr9:uid="{484A9B7F-7C5F-4274-BA19-597F3B11217A}"/>
+    <tableStyle name="表样式 2" pivot="0" count="0" xr9:uid="{B1451224-A6FF-4592-BC65-DA94B54BD5BD}"/>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="totalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowStripe" dxfId="12"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="10"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="9"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="8"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="7"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="6"/>
-      <tableStyleElement type="pageFieldValues" dxfId="5"/>
+      <tableStyleElement type="headerRow" dxfId="29"/>
+      <tableStyleElement type="totalRow" dxfId="28"/>
+      <tableStyleElement type="firstRowStripe" dxfId="27"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="26"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="25"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="24"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="23"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="22"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="21"/>
+      <tableStyleElement type="pageFieldValues" dxfId="20"/>
     </tableStyle>
   </tableStyles>
   <colors>
     <mruColors>
-      <color rgb="FFDDEBF7"/>
-      <color rgb="FF000000"/>
+      <color rgb="00DDEBF7"/>
+      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="A2:D38" headerRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A2:D57" headerRowCount="0" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="关联线索类型" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="法条编号" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="核心内容" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="关联场景（12345高频投诉类型）" dataDxfId="1"/>
+    <tableColumn id="1" name="关联线索类型" dataDxfId="0"/>
+    <tableColumn id="2" name="法条编号" dataDxfId="1"/>
+    <tableColumn id="3" name="核心内容" dataDxfId="2"/>
+    <tableColumn id="4" name="关联场景（12345高频投诉类型）" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStylePreset5_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="表2" displayName="表2" ref="E1:E31" totalsRowShown="0">
-  <autoFilter ref="E1:E31" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表2" displayName="表2" ref="E1:E31" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="E1:E31" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="列1" dataDxfId="0"/>
+    <tableColumn id="1" name="列1" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="表样式 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1702,24 +2609,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultColWidth="19.36328125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr defaultColWidth="19.3893805309735" defaultRowHeight="15.75" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.36328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="36.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.36328125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="19.36328125" style="1"/>
+    <col min="1" max="1" width="17.1592920353982" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.0088495575221" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.353982300885" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.8407079646018" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="19.3893805309735" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.5" x14ac:dyDescent="0.25">
+    <row r="1" ht="17.6" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1732,562 +2638,828 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" ht="110.25" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="63" spans="1:6">
+      <c r="A3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" ht="47.25" spans="1:6">
+      <c r="A4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" ht="47.25" spans="1:6">
+      <c r="A5" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" ht="31.5" spans="1:6">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" ht="63" spans="1:6">
+      <c r="A7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" ht="78.75" spans="1:6">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" ht="126" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" ht="173.25" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" ht="299.25" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" ht="236.25" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" ht="252" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="13"/>
+    </row>
+    <row r="14" ht="189" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" ht="362.25" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" ht="204.75" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" ht="330.75" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" ht="157.5" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" ht="330.75" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" ht="267.75" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" ht="189" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" ht="141.75" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" ht="141.75" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" ht="330.75" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" ht="409.5" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" ht="220.5" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" ht="346.5" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" ht="110.25" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" ht="110.25" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" ht="141.75" spans="1:5">
+      <c r="A30" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" ht="63" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" ht="47.25" spans="1:5">
+      <c r="A32" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" ht="63" spans="1:4">
+      <c r="A33" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" ht="94.5" spans="1:4">
+      <c r="A34" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" ht="110.25" spans="1:4">
+      <c r="A35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" ht="94.5" spans="1:4">
+      <c r="A36" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" ht="94.5" spans="1:4">
+      <c r="A37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" ht="126" spans="1:4">
+      <c r="A38" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" ht="141.75" spans="1:4">
+      <c r="A39" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2"/>
-    </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3"/>
-    </row>
-    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4"/>
-    </row>
-    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6"/>
-    </row>
-    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7"/>
-    </row>
-    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8"/>
-    </row>
-    <row r="9" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9"/>
-    </row>
-    <row r="10" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10"/>
-    </row>
-    <row r="11" spans="1:6" ht="135" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12"/>
-    </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13"/>
-      <c r="F13" s="15"/>
-    </row>
-    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14"/>
-    </row>
-    <row r="15" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15"/>
-    </row>
-    <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16"/>
-    </row>
-    <row r="17" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17"/>
-    </row>
-    <row r="18" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18"/>
-    </row>
-    <row r="19" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19"/>
-    </row>
-    <row r="20" spans="1:5" ht="135" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20"/>
-    </row>
-    <row r="21" spans="1:5" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21"/>
-    </row>
-    <row r="22" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22"/>
-    </row>
-    <row r="23" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23"/>
-    </row>
-    <row r="24" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24"/>
-    </row>
-    <row r="25" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25"/>
-    </row>
-    <row r="26" spans="1:5" ht="122.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26"/>
-    </row>
-    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27"/>
-    </row>
-    <row r="28" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28"/>
-    </row>
-    <row r="29" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29"/>
-    </row>
-    <row r="30" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A30" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30"/>
-    </row>
-    <row r="31" spans="1:5" ht="60" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31"/>
-    </row>
-    <row r="32" spans="1:5" ht="90" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" s="24" t="s">
+      <c r="D39" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" ht="78.75" spans="1:4">
+      <c r="A40" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="225" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="90" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>118</v>
+      <c r="B40" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" ht="63" spans="1:4">
+      <c r="A41" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" ht="94.5" spans="1:4">
+      <c r="A42" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" ht="94.5" spans="1:4">
+      <c r="A43" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" ht="94.5" spans="1:4">
+      <c r="A44" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" ht="129" spans="1:4">
+      <c r="A45" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" ht="31.5" spans="1:4">
+      <c r="A46" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" ht="126" spans="1:4">
+      <c r="A47" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" ht="94.5" spans="1:4">
+      <c r="A48" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" ht="94.5" spans="1:4">
+      <c r="A49" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="50" ht="63" spans="1:4">
+      <c r="A50" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" ht="94.5" spans="1:4">
+      <c r="A51" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="52" ht="94.5" spans="1:4">
+      <c r="A52" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" ht="173.25" spans="1:4">
+      <c r="A53" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="D53" s="24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" ht="94.5" spans="1:4">
+      <c r="A54" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" ht="63" spans="1:4">
+      <c r="A55" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" ht="236.25" spans="1:4">
+      <c r="A56" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" ht="94.5" spans="1:4">
+      <c r="A57" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
